--- a/UTCUTS/A1_Outputs/previous_version_1/A-O_Parametrization_PREV1.xlsx
+++ b/UTCUTS/A1_Outputs/previous_version_1/A-O_Parametrization_PREV1.xlsx
@@ -29878,7 +29878,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F671BB29-0C5F-4107-938A-E10961F7E797}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFAFFA8E-BE5C-4A6C-B6A6-748018D802CD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
